--- a/test/appium_tests/test_file/test_login.xlsx
+++ b/test/appium_tests/test_file/test_login.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nam3\hocky2\KTPM\app_music\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nam3\hocky2\kiemthu_giuaky\app_music\test\appium_tests\test_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8494472E-C2BD-4880-84B7-828242A62BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52F86ED-D685-4BB3-8FE9-3677E150E198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
